--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2018_biobio.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_mediabrut_a_2018_biobio.xlsx
@@ -93,7 +93,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 13:46</t>
+    <t xml:space="preserve">2026-09-24 00:37</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -672,7 +672,7 @@
         <v>-0.05</v>
       </c>
       <c r="F8" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G8" s="2" t="n">
         <v>-0.34</v>
@@ -695,10 +695,10 @@
         <v>-0.06</v>
       </c>
       <c r="F9" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G9" s="2" t="n">
-        <v>-0.18</v>
+        <v>-0.19</v>
       </c>
     </row>
     <row r="10">
@@ -715,10 +715,10 @@
         <v>33</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.02</v>
+        <v>-0.01</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G10" s="2" t="n">
         <v>-0.18</v>
@@ -732,19 +732,19 @@
         <v>16</v>
       </c>
       <c r="C11" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
       <c r="D11" s="2" t="n">
         <v>33</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.01</v>
+        <v>0</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>-0.1</v>
+        <v>-0.09</v>
       </c>
     </row>
     <row r="12">
